--- a/artfynd/A 38964-2026 artfynd.xlsx
+++ b/artfynd/A 38964-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137383639</v>
       </c>
       <c r="B2" t="n">
-        <v>87465</v>
+        <v>87470</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>137381399</v>
       </c>
       <c r="B3" t="n">
-        <v>96624</v>
+        <v>96630</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -887,7 +887,7 @@
         <v>137381652</v>
       </c>
       <c r="B4" t="n">
-        <v>96624</v>
+        <v>96630</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -989,7 +989,7 @@
         <v>137382993</v>
       </c>
       <c r="B5" t="n">
-        <v>93475</v>
+        <v>93481</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1091,7 +1091,7 @@
         <v>137382344</v>
       </c>
       <c r="B6" t="n">
-        <v>93134</v>
+        <v>93140</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1193,7 +1193,7 @@
         <v>137382932</v>
       </c>
       <c r="B7" t="n">
-        <v>93134</v>
+        <v>93140</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1295,7 +1295,7 @@
         <v>137383671</v>
       </c>
       <c r="B8" t="n">
-        <v>93134</v>
+        <v>93140</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1397,7 +1397,7 @@
         <v>137381568</v>
       </c>
       <c r="B9" t="n">
-        <v>93499</v>
+        <v>93505</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1499,7 +1499,7 @@
         <v>137383020</v>
       </c>
       <c r="B10" t="n">
-        <v>93499</v>
+        <v>93505</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1601,7 +1601,7 @@
         <v>137383070</v>
       </c>
       <c r="B11" t="n">
-        <v>93499</v>
+        <v>93505</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1703,7 +1703,7 @@
         <v>137383084</v>
       </c>
       <c r="B12" t="n">
-        <v>93499</v>
+        <v>93505</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1805,7 +1805,7 @@
         <v>137383885</v>
       </c>
       <c r="B13" t="n">
-        <v>93499</v>
+        <v>93505</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1907,7 +1907,7 @@
         <v>137384195</v>
       </c>
       <c r="B14" t="n">
-        <v>93499</v>
+        <v>93505</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2009,7 +2009,7 @@
         <v>137384321</v>
       </c>
       <c r="B15" t="n">
-        <v>93501</v>
+        <v>93507</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2111,7 +2111,7 @@
         <v>137384342</v>
       </c>
       <c r="B16" t="n">
-        <v>57955</v>
+        <v>57956</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2213,7 +2213,7 @@
         <v>137381590</v>
       </c>
       <c r="B17" t="n">
-        <v>58195</v>
+        <v>58196</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2316,7 +2316,7 @@
         <v>137381294</v>
       </c>
       <c r="B18" t="n">
-        <v>99390</v>
+        <v>99396</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2418,7 +2418,7 @@
         <v>137381529</v>
       </c>
       <c r="B19" t="n">
-        <v>99390</v>
+        <v>99396</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2520,7 +2520,7 @@
         <v>137381932</v>
       </c>
       <c r="B20" t="n">
-        <v>99390</v>
+        <v>99396</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2622,7 +2622,7 @@
         <v>137382274</v>
       </c>
       <c r="B21" t="n">
-        <v>99390</v>
+        <v>99396</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2724,7 +2724,7 @@
         <v>137383002</v>
       </c>
       <c r="B22" t="n">
-        <v>99390</v>
+        <v>99396</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2826,7 +2826,7 @@
         <v>137382386</v>
       </c>
       <c r="B23" t="n">
-        <v>99435</v>
+        <v>99441</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2928,7 +2928,7 @@
         <v>137383133</v>
       </c>
       <c r="B24" t="n">
-        <v>104945</v>
+        <v>104951</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3030,7 +3030,7 @@
         <v>137383165</v>
       </c>
       <c r="B25" t="n">
-        <v>104945</v>
+        <v>104951</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3132,7 +3132,7 @@
         <v>137381381</v>
       </c>
       <c r="B26" t="n">
-        <v>101628</v>
+        <v>101634</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3234,7 +3234,7 @@
         <v>137383104</v>
       </c>
       <c r="B27" t="n">
-        <v>101628</v>
+        <v>101634</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>

--- a/artfynd/A 38964-2026 artfynd.xlsx
+++ b/artfynd/A 38964-2026 artfynd.xlsx
@@ -2928,7 +2928,7 @@
         <v>137383133</v>
       </c>
       <c r="B24" t="n">
-        <v>104951</v>
+        <v>104952</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3030,7 +3030,7 @@
         <v>137383165</v>
       </c>
       <c r="B25" t="n">
-        <v>104951</v>
+        <v>104952</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>

--- a/artfynd/A 38964-2026 artfynd.xlsx
+++ b/artfynd/A 38964-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137383639</v>
       </c>
       <c r="B2" t="n">
-        <v>87470</v>
+        <v>87481</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>137381399</v>
       </c>
       <c r="B3" t="n">
-        <v>96630</v>
+        <v>96642</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -887,7 +887,7 @@
         <v>137381652</v>
       </c>
       <c r="B4" t="n">
-        <v>96630</v>
+        <v>96642</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -989,7 +989,7 @@
         <v>137382993</v>
       </c>
       <c r="B5" t="n">
-        <v>93481</v>
+        <v>93493</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1091,7 +1091,7 @@
         <v>137382344</v>
       </c>
       <c r="B6" t="n">
-        <v>93140</v>
+        <v>93152</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1193,7 +1193,7 @@
         <v>137382932</v>
       </c>
       <c r="B7" t="n">
-        <v>93140</v>
+        <v>93152</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1295,7 +1295,7 @@
         <v>137383671</v>
       </c>
       <c r="B8" t="n">
-        <v>93140</v>
+        <v>93152</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1397,7 +1397,7 @@
         <v>137381568</v>
       </c>
       <c r="B9" t="n">
-        <v>93505</v>
+        <v>93517</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1499,7 +1499,7 @@
         <v>137383020</v>
       </c>
       <c r="B10" t="n">
-        <v>93505</v>
+        <v>93517</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1601,7 +1601,7 @@
         <v>137383070</v>
       </c>
       <c r="B11" t="n">
-        <v>93505</v>
+        <v>93517</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1703,7 +1703,7 @@
         <v>137383084</v>
       </c>
       <c r="B12" t="n">
-        <v>93505</v>
+        <v>93517</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1805,7 +1805,7 @@
         <v>137383885</v>
       </c>
       <c r="B13" t="n">
-        <v>93505</v>
+        <v>93517</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1907,7 +1907,7 @@
         <v>137384195</v>
       </c>
       <c r="B14" t="n">
-        <v>93505</v>
+        <v>93517</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2009,7 +2009,7 @@
         <v>137384321</v>
       </c>
       <c r="B15" t="n">
-        <v>93507</v>
+        <v>93519</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2316,7 +2316,7 @@
         <v>137381294</v>
       </c>
       <c r="B18" t="n">
-        <v>99396</v>
+        <v>99408</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2418,7 +2418,7 @@
         <v>137381529</v>
       </c>
       <c r="B19" t="n">
-        <v>99396</v>
+        <v>99408</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2520,7 +2520,7 @@
         <v>137381932</v>
       </c>
       <c r="B20" t="n">
-        <v>99396</v>
+        <v>99408</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2622,7 +2622,7 @@
         <v>137382274</v>
       </c>
       <c r="B21" t="n">
-        <v>99396</v>
+        <v>99408</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2724,7 +2724,7 @@
         <v>137383002</v>
       </c>
       <c r="B22" t="n">
-        <v>99396</v>
+        <v>99408</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2826,7 +2826,7 @@
         <v>137382386</v>
       </c>
       <c r="B23" t="n">
-        <v>99441</v>
+        <v>99453</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2928,7 +2928,7 @@
         <v>137383133</v>
       </c>
       <c r="B24" t="n">
-        <v>104952</v>
+        <v>104964</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3030,7 +3030,7 @@
         <v>137383165</v>
       </c>
       <c r="B25" t="n">
-        <v>104952</v>
+        <v>104964</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3132,7 +3132,7 @@
         <v>137381381</v>
       </c>
       <c r="B26" t="n">
-        <v>101634</v>
+        <v>101646</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3234,7 +3234,7 @@
         <v>137383104</v>
       </c>
       <c r="B27" t="n">
-        <v>101634</v>
+        <v>101646</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>

--- a/artfynd/A 38964-2026 artfynd.xlsx
+++ b/artfynd/A 38964-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137383639</v>
       </c>
       <c r="B2" t="n">
-        <v>87481</v>
+        <v>87482</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>137381399</v>
       </c>
       <c r="B3" t="n">
-        <v>96642</v>
+        <v>96643</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -887,7 +887,7 @@
         <v>137381652</v>
       </c>
       <c r="B4" t="n">
-        <v>96642</v>
+        <v>96643</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -989,7 +989,7 @@
         <v>137382993</v>
       </c>
       <c r="B5" t="n">
-        <v>93493</v>
+        <v>93494</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1091,7 +1091,7 @@
         <v>137382344</v>
       </c>
       <c r="B6" t="n">
-        <v>93152</v>
+        <v>93153</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1193,7 +1193,7 @@
         <v>137382932</v>
       </c>
       <c r="B7" t="n">
-        <v>93152</v>
+        <v>93153</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1295,7 +1295,7 @@
         <v>137383671</v>
       </c>
       <c r="B8" t="n">
-        <v>93152</v>
+        <v>93153</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1397,7 +1397,7 @@
         <v>137381568</v>
       </c>
       <c r="B9" t="n">
-        <v>93517</v>
+        <v>93518</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1499,7 +1499,7 @@
         <v>137383020</v>
       </c>
       <c r="B10" t="n">
-        <v>93517</v>
+        <v>93518</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1601,7 +1601,7 @@
         <v>137383070</v>
       </c>
       <c r="B11" t="n">
-        <v>93517</v>
+        <v>93518</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1703,7 +1703,7 @@
         <v>137383084</v>
       </c>
       <c r="B12" t="n">
-        <v>93517</v>
+        <v>93518</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1805,7 +1805,7 @@
         <v>137383885</v>
       </c>
       <c r="B13" t="n">
-        <v>93517</v>
+        <v>93518</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1907,7 +1907,7 @@
         <v>137384195</v>
       </c>
       <c r="B14" t="n">
-        <v>93517</v>
+        <v>93518</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2009,7 +2009,7 @@
         <v>137384321</v>
       </c>
       <c r="B15" t="n">
-        <v>93519</v>
+        <v>93520</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2316,7 +2316,7 @@
         <v>137381294</v>
       </c>
       <c r="B18" t="n">
-        <v>99408</v>
+        <v>99409</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2418,7 +2418,7 @@
         <v>137381529</v>
       </c>
       <c r="B19" t="n">
-        <v>99408</v>
+        <v>99409</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2520,7 +2520,7 @@
         <v>137381932</v>
       </c>
       <c r="B20" t="n">
-        <v>99408</v>
+        <v>99409</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2622,7 +2622,7 @@
         <v>137382274</v>
       </c>
       <c r="B21" t="n">
-        <v>99408</v>
+        <v>99409</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2724,7 +2724,7 @@
         <v>137383002</v>
       </c>
       <c r="B22" t="n">
-        <v>99408</v>
+        <v>99409</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2826,7 +2826,7 @@
         <v>137382386</v>
       </c>
       <c r="B23" t="n">
-        <v>99453</v>
+        <v>99454</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2928,7 +2928,7 @@
         <v>137383133</v>
       </c>
       <c r="B24" t="n">
-        <v>104964</v>
+        <v>104965</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3030,7 +3030,7 @@
         <v>137383165</v>
       </c>
       <c r="B25" t="n">
-        <v>104964</v>
+        <v>104965</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3132,7 +3132,7 @@
         <v>137381381</v>
       </c>
       <c r="B26" t="n">
-        <v>101646</v>
+        <v>101647</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3234,7 +3234,7 @@
         <v>137383104</v>
       </c>
       <c r="B27" t="n">
-        <v>101646</v>
+        <v>101647</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>

--- a/artfynd/A 38964-2026 artfynd.xlsx
+++ b/artfynd/A 38964-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137383639</v>
       </c>
       <c r="B2" t="n">
-        <v>87482</v>
+        <v>87485</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>137381399</v>
       </c>
       <c r="B3" t="n">
-        <v>96643</v>
+        <v>96646</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -887,7 +887,7 @@
         <v>137381652</v>
       </c>
       <c r="B4" t="n">
-        <v>96643</v>
+        <v>96646</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -989,7 +989,7 @@
         <v>137382993</v>
       </c>
       <c r="B5" t="n">
-        <v>93494</v>
+        <v>93497</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1091,7 +1091,7 @@
         <v>137382344</v>
       </c>
       <c r="B6" t="n">
-        <v>93153</v>
+        <v>93156</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1193,7 +1193,7 @@
         <v>137382932</v>
       </c>
       <c r="B7" t="n">
-        <v>93153</v>
+        <v>93156</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1295,7 +1295,7 @@
         <v>137383671</v>
       </c>
       <c r="B8" t="n">
-        <v>93153</v>
+        <v>93156</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1397,7 +1397,7 @@
         <v>137381568</v>
       </c>
       <c r="B9" t="n">
-        <v>93518</v>
+        <v>93521</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1499,7 +1499,7 @@
         <v>137383020</v>
       </c>
       <c r="B10" t="n">
-        <v>93518</v>
+        <v>93521</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1601,7 +1601,7 @@
         <v>137383070</v>
       </c>
       <c r="B11" t="n">
-        <v>93518</v>
+        <v>93521</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1703,7 +1703,7 @@
         <v>137383084</v>
       </c>
       <c r="B12" t="n">
-        <v>93518</v>
+        <v>93521</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1805,7 +1805,7 @@
         <v>137383885</v>
       </c>
       <c r="B13" t="n">
-        <v>93518</v>
+        <v>93521</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1907,7 +1907,7 @@
         <v>137384195</v>
       </c>
       <c r="B14" t="n">
-        <v>93518</v>
+        <v>93521</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2009,7 +2009,7 @@
         <v>137384321</v>
       </c>
       <c r="B15" t="n">
-        <v>93520</v>
+        <v>93523</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2316,7 +2316,7 @@
         <v>137381294</v>
       </c>
       <c r="B18" t="n">
-        <v>99409</v>
+        <v>99412</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2418,7 +2418,7 @@
         <v>137381529</v>
       </c>
       <c r="B19" t="n">
-        <v>99409</v>
+        <v>99412</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2520,7 +2520,7 @@
         <v>137381932</v>
       </c>
       <c r="B20" t="n">
-        <v>99409</v>
+        <v>99412</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2622,7 +2622,7 @@
         <v>137382274</v>
       </c>
       <c r="B21" t="n">
-        <v>99409</v>
+        <v>99412</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2724,7 +2724,7 @@
         <v>137383002</v>
       </c>
       <c r="B22" t="n">
-        <v>99409</v>
+        <v>99412</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2826,7 +2826,7 @@
         <v>137382386</v>
       </c>
       <c r="B23" t="n">
-        <v>99454</v>
+        <v>99457</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2928,7 +2928,7 @@
         <v>137383133</v>
       </c>
       <c r="B24" t="n">
-        <v>104965</v>
+        <v>104968</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3030,7 +3030,7 @@
         <v>137383165</v>
       </c>
       <c r="B25" t="n">
-        <v>104965</v>
+        <v>104968</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3132,7 +3132,7 @@
         <v>137381381</v>
       </c>
       <c r="B26" t="n">
-        <v>101647</v>
+        <v>101650</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3234,7 +3234,7 @@
         <v>137383104</v>
       </c>
       <c r="B27" t="n">
-        <v>101647</v>
+        <v>101650</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>

--- a/artfynd/A 38964-2026 artfynd.xlsx
+++ b/artfynd/A 38964-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ27"/>
+  <dimension ref="A1:AZ37"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -986,32 +986,32 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>137382993</v>
+        <v>137505156</v>
       </c>
       <c r="B5" t="n">
-        <v>93497</v>
+        <v>87557</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>4366</v>
+        <v>3674</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Anisspindling</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Cortinarius odorifer</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Banker</t>
+          <t>Britzelm.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1021,10 +1021,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>678182</v>
+        <v>678191</v>
       </c>
       <c r="R5" t="n">
-        <v>6691433</v>
+        <v>6691004</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1051,12 +1051,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2026-10-21</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2026-10-21</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1082,38 +1082,38 @@
       <c r="AY5" t="inlineStr"/>
       <c r="AZ5" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137382993</t>
+          <t>https://artportalen.se/Sighting/137505156</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>137382344</v>
+        <v>137382993</v>
       </c>
       <c r="B6" t="n">
-        <v>93156</v>
+        <v>93497</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>4769</v>
+        <v>4366</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Svavelriska</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Lactarius scrobiculatus</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Scop.) Fr.</t>
+          <t>Banker</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1123,10 +1123,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>678353</v>
+        <v>678182</v>
       </c>
       <c r="R6" t="n">
-        <v>6691308</v>
+        <v>6691433</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1184,13 +1184,13 @@
       <c r="AY6" t="inlineStr"/>
       <c r="AZ6" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137382344</t>
+          <t>https://artportalen.se/Sighting/137382993</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>137382932</v>
+        <v>137382344</v>
       </c>
       <c r="B7" t="n">
         <v>93156</v>
@@ -1225,10 +1225,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>678241</v>
+        <v>678353</v>
       </c>
       <c r="R7" t="n">
-        <v>6691404</v>
+        <v>6691308</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1286,13 +1286,13 @@
       <c r="AY7" t="inlineStr"/>
       <c r="AZ7" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137382932</t>
+          <t>https://artportalen.se/Sighting/137382344</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>137383671</v>
+        <v>137382932</v>
       </c>
       <c r="B8" t="n">
         <v>93156</v>
@@ -1327,10 +1327,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>678187</v>
+        <v>678241</v>
       </c>
       <c r="R8" t="n">
-        <v>6691535</v>
+        <v>6691404</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1388,38 +1388,38 @@
       <c r="AY8" t="inlineStr"/>
       <c r="AZ8" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137383671</t>
+          <t>https://artportalen.se/Sighting/137382932</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>137381568</v>
+        <v>137383671</v>
       </c>
       <c r="B9" t="n">
-        <v>93521</v>
+        <v>93156</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>5964</v>
+        <v>4769</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) P.Karst.</t>
+          <t>(Scop.) Fr.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1429,10 +1429,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>678426</v>
+        <v>678187</v>
       </c>
       <c r="R9" t="n">
-        <v>6691282</v>
+        <v>6691535</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1490,13 +1490,13 @@
       <c r="AY9" t="inlineStr"/>
       <c r="AZ9" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137381568</t>
+          <t>https://artportalen.se/Sighting/137383671</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>137383020</v>
+        <v>137381568</v>
       </c>
       <c r="B10" t="n">
         <v>93521</v>
@@ -1531,10 +1531,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>678178</v>
+        <v>678426</v>
       </c>
       <c r="R10" t="n">
-        <v>6691426</v>
+        <v>6691282</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1592,13 +1592,13 @@
       <c r="AY10" t="inlineStr"/>
       <c r="AZ10" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137383020</t>
+          <t>https://artportalen.se/Sighting/137381568</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>137383070</v>
+        <v>137383020</v>
       </c>
       <c r="B11" t="n">
         <v>93521</v>
@@ -1633,10 +1633,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>678175</v>
+        <v>678178</v>
       </c>
       <c r="R11" t="n">
-        <v>6691446</v>
+        <v>6691426</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1694,13 +1694,13 @@
       <c r="AY11" t="inlineStr"/>
       <c r="AZ11" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137383070</t>
+          <t>https://artportalen.se/Sighting/137383020</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>137383084</v>
+        <v>137383070</v>
       </c>
       <c r="B12" t="n">
         <v>93521</v>
@@ -1735,10 +1735,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>678185</v>
+        <v>678175</v>
       </c>
       <c r="R12" t="n">
-        <v>6691444</v>
+        <v>6691446</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1796,13 +1796,13 @@
       <c r="AY12" t="inlineStr"/>
       <c r="AZ12" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137383084</t>
+          <t>https://artportalen.se/Sighting/137383070</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>137383885</v>
+        <v>137383084</v>
       </c>
       <c r="B13" t="n">
         <v>93521</v>
@@ -1837,10 +1837,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>678253</v>
+        <v>678185</v>
       </c>
       <c r="R13" t="n">
-        <v>6691428</v>
+        <v>6691444</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1898,13 +1898,13 @@
       <c r="AY13" t="inlineStr"/>
       <c r="AZ13" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137383885</t>
+          <t>https://artportalen.se/Sighting/137383084</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>137384195</v>
+        <v>137383885</v>
       </c>
       <c r="B14" t="n">
         <v>93521</v>
@@ -1939,10 +1939,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>678327</v>
+        <v>678253</v>
       </c>
       <c r="R14" t="n">
-        <v>6691430</v>
+        <v>6691428</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2000,16 +2000,16 @@
       <c r="AY14" t="inlineStr"/>
       <c r="AZ14" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137384195</t>
+          <t>https://artportalen.se/Sighting/137383885</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>137384321</v>
+        <v>137384195</v>
       </c>
       <c r="B15" t="n">
-        <v>93523</v>
+        <v>93521</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2017,21 +2017,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>5966</v>
+        <v>5964</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(L.) P.Karst.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2041,10 +2041,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>678405</v>
+        <v>678327</v>
       </c>
       <c r="R15" t="n">
-        <v>6691420</v>
+        <v>6691430</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2102,16 +2102,16 @@
       <c r="AY15" t="inlineStr"/>
       <c r="AZ15" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137384321</t>
+          <t>https://artportalen.se/Sighting/137384195</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>137384342</v>
+        <v>137504562</v>
       </c>
       <c r="B16" t="n">
-        <v>57956</v>
+        <v>93522</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2119,21 +2119,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>100001</v>
+        <v>5964</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Duvhök</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Astur gentilis</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) P.Karst.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2143,13 +2143,13 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>678403</v>
+        <v>678159</v>
       </c>
       <c r="R16" t="n">
-        <v>6691418</v>
+        <v>6691027</v>
       </c>
       <c r="S16" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2173,12 +2173,12 @@
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>2026-10-21</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>2026-10-21</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2204,16 +2204,16 @@
       <c r="AY16" t="inlineStr"/>
       <c r="AZ16" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137384342</t>
+          <t>https://artportalen.se/Sighting/137504562</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>137381590</v>
+        <v>137504573</v>
       </c>
       <c r="B17" t="n">
-        <v>58196</v>
+        <v>93522</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2221,38 +2221,37 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>103021</v>
+        <v>5964</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(L.) P.Karst.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
-      <c r="M17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
           <t>Duderö, Upl</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>678450</v>
+        <v>678130</v>
       </c>
       <c r="R17" t="n">
-        <v>6691263</v>
+        <v>6691055</v>
       </c>
       <c r="S17" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2276,12 +2275,12 @@
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>2026-10-21</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>2026-10-21</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2307,38 +2306,38 @@
       <c r="AY17" t="inlineStr"/>
       <c r="AZ17" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137381590</t>
+          <t>https://artportalen.se/Sighting/137504573</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>137381294</v>
+        <v>137504629</v>
       </c>
       <c r="B18" t="n">
-        <v>99412</v>
+        <v>93522</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>219798</v>
+        <v>5964</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Epipactis helleborine</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
+          <t>(L.) P.Karst.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2348,10 +2347,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>678417</v>
+        <v>678118</v>
       </c>
       <c r="R18" t="n">
-        <v>6691217</v>
+        <v>6691084</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2378,12 +2377,12 @@
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>2026-10-21</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>2026-10-21</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2409,38 +2408,38 @@
       <c r="AY18" t="inlineStr"/>
       <c r="AZ18" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137381294</t>
+          <t>https://artportalen.se/Sighting/137504629</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>137381529</v>
+        <v>137504680</v>
       </c>
       <c r="B19" t="n">
-        <v>99412</v>
+        <v>93522</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>219798</v>
+        <v>5964</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Epipactis helleborine</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
+          <t>(L.) P.Karst.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2450,10 +2449,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>678423</v>
+        <v>678167</v>
       </c>
       <c r="R19" t="n">
-        <v>6691254</v>
+        <v>6691044</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2480,12 +2479,12 @@
       </c>
       <c r="Y19" t="inlineStr">
         <is>
-          <t>2026-10-21</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>2026-10-21</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2511,38 +2510,38 @@
       <c r="AY19" t="inlineStr"/>
       <c r="AZ19" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137381529</t>
+          <t>https://artportalen.se/Sighting/137504680</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>137381932</v>
+        <v>137505200</v>
       </c>
       <c r="B20" t="n">
-        <v>99412</v>
+        <v>93522</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>219798</v>
+        <v>5964</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Epipactis helleborine</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
+          <t>(L.) P.Karst.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2552,10 +2551,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>678415</v>
+        <v>678198</v>
       </c>
       <c r="R20" t="n">
-        <v>6691285</v>
+        <v>6691029</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2582,12 +2581,12 @@
       </c>
       <c r="Y20" t="inlineStr">
         <is>
-          <t>2026-10-21</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
         <is>
-          <t>2026-10-21</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2613,38 +2612,38 @@
       <c r="AY20" t="inlineStr"/>
       <c r="AZ20" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137381932</t>
+          <t>https://artportalen.se/Sighting/137505200</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>137382274</v>
+        <v>137384321</v>
       </c>
       <c r="B21" t="n">
-        <v>99412</v>
+        <v>93523</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>219798</v>
+        <v>5966</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Epipactis helleborine</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2654,10 +2653,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>678377</v>
+        <v>678405</v>
       </c>
       <c r="R21" t="n">
-        <v>6691313</v>
+        <v>6691420</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2715,38 +2714,38 @@
       <c r="AY21" t="inlineStr"/>
       <c r="AZ21" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137382274</t>
+          <t>https://artportalen.se/Sighting/137384321</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>137383002</v>
+        <v>137384342</v>
       </c>
       <c r="B22" t="n">
-        <v>99412</v>
+        <v>57956</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>219798</v>
+        <v>100001</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Duvhök</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Epipactis helleborine</t>
+          <t>Astur gentilis</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2756,13 +2755,13 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>678176</v>
+        <v>678403</v>
       </c>
       <c r="R22" t="n">
-        <v>6691424</v>
+        <v>6691418</v>
       </c>
       <c r="S22" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -2817,54 +2816,55 @@
       <c r="AY22" t="inlineStr"/>
       <c r="AZ22" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137383002</t>
+          <t>https://artportalen.se/Sighting/137384342</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>137382386</v>
+        <v>137381590</v>
       </c>
       <c r="B23" t="n">
-        <v>99457</v>
+        <v>58196</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>219862</v>
+        <v>103021</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Nästrot</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Neottia nidus-avis</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
+      <c r="M23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
           <t>Duderö, Upl</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>678326</v>
+        <v>678450</v>
       </c>
       <c r="R23" t="n">
-        <v>6691332</v>
+        <v>6691263</v>
       </c>
       <c r="S23" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -2919,16 +2919,16 @@
       <c r="AY23" t="inlineStr"/>
       <c r="AZ23" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137382386</t>
+          <t>https://artportalen.se/Sighting/137381590</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>137383133</v>
+        <v>137381294</v>
       </c>
       <c r="B24" t="n">
-        <v>104968</v>
+        <v>99412</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2936,21 +2936,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>222412</v>
+        <v>219798</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Tibast</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Daphne mezereum</t>
+          <t>Epipactis helleborine</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Crantz</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -2960,10 +2960,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>678135</v>
+        <v>678417</v>
       </c>
       <c r="R24" t="n">
-        <v>6691495</v>
+        <v>6691217</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3021,16 +3021,16 @@
       <c r="AY24" t="inlineStr"/>
       <c r="AZ24" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137383133</t>
+          <t>https://artportalen.se/Sighting/137381294</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>137383165</v>
+        <v>137381529</v>
       </c>
       <c r="B25" t="n">
-        <v>104968</v>
+        <v>99412</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3038,21 +3038,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>222412</v>
+        <v>219798</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Tibast</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Daphne mezereum</t>
+          <t>Epipactis helleborine</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Crantz</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3062,10 +3062,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>678105</v>
+        <v>678423</v>
       </c>
       <c r="R25" t="n">
-        <v>6691485</v>
+        <v>6691254</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3123,16 +3123,16 @@
       <c r="AY25" t="inlineStr"/>
       <c r="AZ25" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137383165</t>
+          <t>https://artportalen.se/Sighting/137381529</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>137381381</v>
+        <v>137381932</v>
       </c>
       <c r="B26" t="n">
-        <v>101650</v>
+        <v>99412</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3140,21 +3140,21 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>222498</v>
+        <v>219798</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Epipactis helleborine</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(L.) Crantz</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3164,10 +3164,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>678430</v>
+        <v>678415</v>
       </c>
       <c r="R26" t="n">
-        <v>6691223</v>
+        <v>6691285</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3225,16 +3225,16 @@
       <c r="AY26" t="inlineStr"/>
       <c r="AZ26" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137381381</t>
+          <t>https://artportalen.se/Sighting/137381932</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>137383104</v>
+        <v>137382274</v>
       </c>
       <c r="B27" t="n">
-        <v>101650</v>
+        <v>99412</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3242,21 +3242,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>222498</v>
+        <v>219798</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Epipactis helleborine</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(L.) Crantz</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3266,10 +3266,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>678175</v>
+        <v>678377</v>
       </c>
       <c r="R27" t="n">
-        <v>6691444</v>
+        <v>6691313</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3326,6 +3326,1026 @@
       </c>
       <c r="AY27" t="inlineStr"/>
       <c r="AZ27" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137382274</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>137383002</v>
+      </c>
+      <c r="B28" t="n">
+        <v>99412</v>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E28" t="n">
+        <v>219798</v>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>Skogsknipprot</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>Epipactis helleborine</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>(L.) Crantz</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr"/>
+      <c r="P28" t="inlineStr">
+        <is>
+          <t>Duderö, Upl</t>
+        </is>
+      </c>
+      <c r="Q28" t="n">
+        <v>678176</v>
+      </c>
+      <c r="R28" t="n">
+        <v>6691424</v>
+      </c>
+      <c r="S28" t="n">
+        <v>10</v>
+      </c>
+      <c r="T28" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U28" t="inlineStr">
+        <is>
+          <t>Östhammar</t>
+        </is>
+      </c>
+      <c r="V28" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W28" t="inlineStr">
+        <is>
+          <t>Börstil</t>
+        </is>
+      </c>
+      <c r="Y28" t="inlineStr">
+        <is>
+          <t>2026-10-21</t>
+        </is>
+      </c>
+      <c r="AA28" t="inlineStr">
+        <is>
+          <t>2026-10-21</t>
+        </is>
+      </c>
+      <c r="AD28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT28" t="inlineStr"/>
+      <c r="AW28" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX28" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY28" t="inlineStr"/>
+      <c r="AZ28" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137383002</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>137504305</v>
+      </c>
+      <c r="B29" t="n">
+        <v>99413</v>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E29" t="n">
+        <v>219798</v>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>Skogsknipprot</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>Epipactis helleborine</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>(L.) Crantz</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr"/>
+      <c r="P29" t="inlineStr">
+        <is>
+          <t>Duderö, Upl</t>
+        </is>
+      </c>
+      <c r="Q29" t="n">
+        <v>678371</v>
+      </c>
+      <c r="R29" t="n">
+        <v>6691166</v>
+      </c>
+      <c r="S29" t="n">
+        <v>10</v>
+      </c>
+      <c r="T29" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U29" t="inlineStr">
+        <is>
+          <t>Östhammar</t>
+        </is>
+      </c>
+      <c r="V29" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W29" t="inlineStr">
+        <is>
+          <t>Börstil</t>
+        </is>
+      </c>
+      <c r="Y29" t="inlineStr">
+        <is>
+          <t>2026-10-28</t>
+        </is>
+      </c>
+      <c r="AA29" t="inlineStr">
+        <is>
+          <t>2026-10-28</t>
+        </is>
+      </c>
+      <c r="AD29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT29" t="inlineStr"/>
+      <c r="AW29" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX29" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY29" t="inlineStr"/>
+      <c r="AZ29" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137504305</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="n">
+        <v>137504400</v>
+      </c>
+      <c r="B30" t="n">
+        <v>99413</v>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E30" t="n">
+        <v>219798</v>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>Skogsknipprot</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>Epipactis helleborine</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>(L.) Crantz</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr"/>
+      <c r="P30" t="inlineStr">
+        <is>
+          <t>Duderö, Upl</t>
+        </is>
+      </c>
+      <c r="Q30" t="n">
+        <v>678367</v>
+      </c>
+      <c r="R30" t="n">
+        <v>6691116</v>
+      </c>
+      <c r="S30" t="n">
+        <v>10</v>
+      </c>
+      <c r="T30" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U30" t="inlineStr">
+        <is>
+          <t>Östhammar</t>
+        </is>
+      </c>
+      <c r="V30" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W30" t="inlineStr">
+        <is>
+          <t>Börstil</t>
+        </is>
+      </c>
+      <c r="Y30" t="inlineStr">
+        <is>
+          <t>2026-10-28</t>
+        </is>
+      </c>
+      <c r="AA30" t="inlineStr">
+        <is>
+          <t>2026-10-28</t>
+        </is>
+      </c>
+      <c r="AD30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT30" t="inlineStr"/>
+      <c r="AW30" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX30" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY30" t="inlineStr"/>
+      <c r="AZ30" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137504400</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="n">
+        <v>137505276</v>
+      </c>
+      <c r="B31" t="n">
+        <v>99413</v>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E31" t="n">
+        <v>219798</v>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>Skogsknipprot</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>Epipactis helleborine</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>(L.) Crantz</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr"/>
+      <c r="P31" t="inlineStr">
+        <is>
+          <t>Duderö, Upl</t>
+        </is>
+      </c>
+      <c r="Q31" t="n">
+        <v>678208</v>
+      </c>
+      <c r="R31" t="n">
+        <v>6691021</v>
+      </c>
+      <c r="S31" t="n">
+        <v>10</v>
+      </c>
+      <c r="T31" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U31" t="inlineStr">
+        <is>
+          <t>Östhammar</t>
+        </is>
+      </c>
+      <c r="V31" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W31" t="inlineStr">
+        <is>
+          <t>Börstil</t>
+        </is>
+      </c>
+      <c r="Y31" t="inlineStr">
+        <is>
+          <t>2026-10-28</t>
+        </is>
+      </c>
+      <c r="AA31" t="inlineStr">
+        <is>
+          <t>2026-10-28</t>
+        </is>
+      </c>
+      <c r="AD31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT31" t="inlineStr"/>
+      <c r="AW31" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX31" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY31" t="inlineStr"/>
+      <c r="AZ31" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137505276</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="n">
+        <v>137382386</v>
+      </c>
+      <c r="B32" t="n">
+        <v>99457</v>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E32" t="n">
+        <v>219862</v>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>Nästrot</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>Neottia nidus-avis</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr"/>
+      <c r="P32" t="inlineStr">
+        <is>
+          <t>Duderö, Upl</t>
+        </is>
+      </c>
+      <c r="Q32" t="n">
+        <v>678326</v>
+      </c>
+      <c r="R32" t="n">
+        <v>6691332</v>
+      </c>
+      <c r="S32" t="n">
+        <v>10</v>
+      </c>
+      <c r="T32" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U32" t="inlineStr">
+        <is>
+          <t>Östhammar</t>
+        </is>
+      </c>
+      <c r="V32" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W32" t="inlineStr">
+        <is>
+          <t>Börstil</t>
+        </is>
+      </c>
+      <c r="Y32" t="inlineStr">
+        <is>
+          <t>2026-10-21</t>
+        </is>
+      </c>
+      <c r="AA32" t="inlineStr">
+        <is>
+          <t>2026-10-21</t>
+        </is>
+      </c>
+      <c r="AD32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT32" t="inlineStr"/>
+      <c r="AW32" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX32" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY32" t="inlineStr"/>
+      <c r="AZ32" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137382386</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="n">
+        <v>137505541</v>
+      </c>
+      <c r="B33" t="n">
+        <v>102567</v>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E33" t="n">
+        <v>221235</v>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>Vårärt</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>Lathyrus vernus</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>(L.) Bernh.</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr"/>
+      <c r="P33" t="inlineStr">
+        <is>
+          <t>Duderö, Upl</t>
+        </is>
+      </c>
+      <c r="Q33" t="n">
+        <v>678288</v>
+      </c>
+      <c r="R33" t="n">
+        <v>6691054</v>
+      </c>
+      <c r="S33" t="n">
+        <v>10</v>
+      </c>
+      <c r="T33" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U33" t="inlineStr">
+        <is>
+          <t>Östhammar</t>
+        </is>
+      </c>
+      <c r="V33" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W33" t="inlineStr">
+        <is>
+          <t>Börstil</t>
+        </is>
+      </c>
+      <c r="Y33" t="inlineStr">
+        <is>
+          <t>2026-10-28</t>
+        </is>
+      </c>
+      <c r="AA33" t="inlineStr">
+        <is>
+          <t>2026-10-28</t>
+        </is>
+      </c>
+      <c r="AD33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT33" t="inlineStr"/>
+      <c r="AW33" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX33" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY33" t="inlineStr"/>
+      <c r="AZ33" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137505541</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="n">
+        <v>137383133</v>
+      </c>
+      <c r="B34" t="n">
+        <v>104968</v>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E34" t="n">
+        <v>222412</v>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>Tibast</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>Daphne mezereum</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr"/>
+      <c r="P34" t="inlineStr">
+        <is>
+          <t>Duderö, Upl</t>
+        </is>
+      </c>
+      <c r="Q34" t="n">
+        <v>678135</v>
+      </c>
+      <c r="R34" t="n">
+        <v>6691495</v>
+      </c>
+      <c r="S34" t="n">
+        <v>10</v>
+      </c>
+      <c r="T34" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U34" t="inlineStr">
+        <is>
+          <t>Östhammar</t>
+        </is>
+      </c>
+      <c r="V34" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W34" t="inlineStr">
+        <is>
+          <t>Börstil</t>
+        </is>
+      </c>
+      <c r="Y34" t="inlineStr">
+        <is>
+          <t>2026-10-21</t>
+        </is>
+      </c>
+      <c r="AA34" t="inlineStr">
+        <is>
+          <t>2026-10-21</t>
+        </is>
+      </c>
+      <c r="AD34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT34" t="inlineStr"/>
+      <c r="AW34" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX34" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY34" t="inlineStr"/>
+      <c r="AZ34" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137383133</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="n">
+        <v>137383165</v>
+      </c>
+      <c r="B35" t="n">
+        <v>104968</v>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E35" t="n">
+        <v>222412</v>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>Tibast</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>Daphne mezereum</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr"/>
+      <c r="P35" t="inlineStr">
+        <is>
+          <t>Duderö, Upl</t>
+        </is>
+      </c>
+      <c r="Q35" t="n">
+        <v>678105</v>
+      </c>
+      <c r="R35" t="n">
+        <v>6691485</v>
+      </c>
+      <c r="S35" t="n">
+        <v>10</v>
+      </c>
+      <c r="T35" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U35" t="inlineStr">
+        <is>
+          <t>Östhammar</t>
+        </is>
+      </c>
+      <c r="V35" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W35" t="inlineStr">
+        <is>
+          <t>Börstil</t>
+        </is>
+      </c>
+      <c r="Y35" t="inlineStr">
+        <is>
+          <t>2026-10-21</t>
+        </is>
+      </c>
+      <c r="AA35" t="inlineStr">
+        <is>
+          <t>2026-10-21</t>
+        </is>
+      </c>
+      <c r="AD35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT35" t="inlineStr"/>
+      <c r="AW35" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX35" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY35" t="inlineStr"/>
+      <c r="AZ35" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137383165</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="n">
+        <v>137381381</v>
+      </c>
+      <c r="B36" t="n">
+        <v>101650</v>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E36" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr"/>
+      <c r="P36" t="inlineStr">
+        <is>
+          <t>Duderö, Upl</t>
+        </is>
+      </c>
+      <c r="Q36" t="n">
+        <v>678430</v>
+      </c>
+      <c r="R36" t="n">
+        <v>6691223</v>
+      </c>
+      <c r="S36" t="n">
+        <v>10</v>
+      </c>
+      <c r="T36" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U36" t="inlineStr">
+        <is>
+          <t>Östhammar</t>
+        </is>
+      </c>
+      <c r="V36" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W36" t="inlineStr">
+        <is>
+          <t>Börstil</t>
+        </is>
+      </c>
+      <c r="Y36" t="inlineStr">
+        <is>
+          <t>2026-10-21</t>
+        </is>
+      </c>
+      <c r="AA36" t="inlineStr">
+        <is>
+          <t>2026-10-21</t>
+        </is>
+      </c>
+      <c r="AD36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT36" t="inlineStr"/>
+      <c r="AW36" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX36" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY36" t="inlineStr"/>
+      <c r="AZ36" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137381381</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="n">
+        <v>137383104</v>
+      </c>
+      <c r="B37" t="n">
+        <v>101650</v>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E37" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr"/>
+      <c r="P37" t="inlineStr">
+        <is>
+          <t>Duderö, Upl</t>
+        </is>
+      </c>
+      <c r="Q37" t="n">
+        <v>678175</v>
+      </c>
+      <c r="R37" t="n">
+        <v>6691444</v>
+      </c>
+      <c r="S37" t="n">
+        <v>10</v>
+      </c>
+      <c r="T37" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U37" t="inlineStr">
+        <is>
+          <t>Östhammar</t>
+        </is>
+      </c>
+      <c r="V37" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W37" t="inlineStr">
+        <is>
+          <t>Börstil</t>
+        </is>
+      </c>
+      <c r="Y37" t="inlineStr">
+        <is>
+          <t>2026-10-21</t>
+        </is>
+      </c>
+      <c r="AA37" t="inlineStr">
+        <is>
+          <t>2026-10-21</t>
+        </is>
+      </c>
+      <c r="AD37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT37" t="inlineStr"/>
+      <c r="AW37" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX37" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY37" t="inlineStr"/>
+      <c r="AZ37" t="inlineStr">
         <is>
           <t>https://artportalen.se/Sighting/137383104</t>
         </is>
@@ -3359,6 +4379,16 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ28" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ29" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ30" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ31" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ32" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ33" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ34" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ35" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ36" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ37" r:id="rId36"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 38964-2026 artfynd.xlsx
+++ b/artfynd/A 38964-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ37"/>
+  <dimension ref="A1:AZ36"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -683,7 +683,7 @@
         <v>137383639</v>
       </c>
       <c r="B2" t="n">
-        <v>87485</v>
+        <v>87489</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>137381399</v>
       </c>
       <c r="B3" t="n">
-        <v>96646</v>
+        <v>96650</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -887,7 +887,7 @@
         <v>137381652</v>
       </c>
       <c r="B4" t="n">
-        <v>96646</v>
+        <v>96650</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -989,7 +989,7 @@
         <v>137505156</v>
       </c>
       <c r="B5" t="n">
-        <v>87557</v>
+        <v>87560</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1091,7 +1091,7 @@
         <v>137382993</v>
       </c>
       <c r="B6" t="n">
-        <v>93497</v>
+        <v>93501</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1193,7 +1193,7 @@
         <v>137382344</v>
       </c>
       <c r="B7" t="n">
-        <v>93156</v>
+        <v>93160</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1295,7 +1295,7 @@
         <v>137382932</v>
       </c>
       <c r="B8" t="n">
-        <v>93156</v>
+        <v>93160</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1397,7 +1397,7 @@
         <v>137383671</v>
       </c>
       <c r="B9" t="n">
-        <v>93156</v>
+        <v>93160</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1499,7 +1499,7 @@
         <v>137381568</v>
       </c>
       <c r="B10" t="n">
-        <v>93521</v>
+        <v>93525</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1601,7 +1601,7 @@
         <v>137383020</v>
       </c>
       <c r="B11" t="n">
-        <v>93521</v>
+        <v>93525</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1703,7 +1703,7 @@
         <v>137383070</v>
       </c>
       <c r="B12" t="n">
-        <v>93521</v>
+        <v>93525</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1805,7 +1805,7 @@
         <v>137383084</v>
       </c>
       <c r="B13" t="n">
-        <v>93521</v>
+        <v>93525</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1907,7 +1907,7 @@
         <v>137383885</v>
       </c>
       <c r="B14" t="n">
-        <v>93521</v>
+        <v>93525</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2009,7 +2009,7 @@
         <v>137384195</v>
       </c>
       <c r="B15" t="n">
-        <v>93521</v>
+        <v>93525</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2111,7 +2111,7 @@
         <v>137504562</v>
       </c>
       <c r="B16" t="n">
-        <v>93522</v>
+        <v>93525</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2213,7 +2213,7 @@
         <v>137504573</v>
       </c>
       <c r="B17" t="n">
-        <v>93522</v>
+        <v>93525</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2315,7 +2315,7 @@
         <v>137504629</v>
       </c>
       <c r="B18" t="n">
-        <v>93522</v>
+        <v>93525</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2417,7 +2417,7 @@
         <v>137504680</v>
       </c>
       <c r="B19" t="n">
-        <v>93522</v>
+        <v>93525</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2519,7 +2519,7 @@
         <v>137505200</v>
       </c>
       <c r="B20" t="n">
-        <v>93522</v>
+        <v>93525</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2621,7 +2621,7 @@
         <v>137384321</v>
       </c>
       <c r="B21" t="n">
-        <v>93523</v>
+        <v>93527</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2720,10 +2720,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>137384342</v>
+        <v>137381590</v>
       </c>
       <c r="B22" t="n">
-        <v>57956</v>
+        <v>58199</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2731,34 +2731,35 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>100001</v>
+        <v>103021</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Duvhök</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Astur gentilis</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
+      <c r="M22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
           <t>Duderö, Upl</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>678403</v>
+        <v>678450</v>
       </c>
       <c r="R22" t="n">
-        <v>6691418</v>
+        <v>6691263</v>
       </c>
       <c r="S22" t="n">
         <v>25</v>
@@ -2816,55 +2817,54 @@
       <c r="AY22" t="inlineStr"/>
       <c r="AZ22" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137384342</t>
+          <t>https://artportalen.se/Sighting/137381590</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>137381590</v>
+        <v>137381294</v>
       </c>
       <c r="B23" t="n">
-        <v>58196</v>
+        <v>99416</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>103021</v>
+        <v>219798</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Epipactis helleborine</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(L.) Crantz</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
-      <c r="M23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
           <t>Duderö, Upl</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>678450</v>
+        <v>678417</v>
       </c>
       <c r="R23" t="n">
-        <v>6691263</v>
+        <v>6691217</v>
       </c>
       <c r="S23" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -2919,16 +2919,16 @@
       <c r="AY23" t="inlineStr"/>
       <c r="AZ23" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137381590</t>
+          <t>https://artportalen.se/Sighting/137381294</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>137381294</v>
+        <v>137381529</v>
       </c>
       <c r="B24" t="n">
-        <v>99412</v>
+        <v>99416</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2960,10 +2960,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>678417</v>
+        <v>678423</v>
       </c>
       <c r="R24" t="n">
-        <v>6691217</v>
+        <v>6691254</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3021,16 +3021,16 @@
       <c r="AY24" t="inlineStr"/>
       <c r="AZ24" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137381294</t>
+          <t>https://artportalen.se/Sighting/137381529</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>137381529</v>
+        <v>137381932</v>
       </c>
       <c r="B25" t="n">
-        <v>99412</v>
+        <v>99416</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3062,10 +3062,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>678423</v>
+        <v>678415</v>
       </c>
       <c r="R25" t="n">
-        <v>6691254</v>
+        <v>6691285</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3123,16 +3123,16 @@
       <c r="AY25" t="inlineStr"/>
       <c r="AZ25" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137381529</t>
+          <t>https://artportalen.se/Sighting/137381932</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>137381932</v>
+        <v>137382274</v>
       </c>
       <c r="B26" t="n">
-        <v>99412</v>
+        <v>99416</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3164,10 +3164,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>678415</v>
+        <v>678377</v>
       </c>
       <c r="R26" t="n">
-        <v>6691285</v>
+        <v>6691313</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3225,16 +3225,16 @@
       <c r="AY26" t="inlineStr"/>
       <c r="AZ26" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137381932</t>
+          <t>https://artportalen.se/Sighting/137382274</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>137382274</v>
+        <v>137383002</v>
       </c>
       <c r="B27" t="n">
-        <v>99412</v>
+        <v>99416</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3266,10 +3266,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>678377</v>
+        <v>678176</v>
       </c>
       <c r="R27" t="n">
-        <v>6691313</v>
+        <v>6691424</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3327,16 +3327,16 @@
       <c r="AY27" t="inlineStr"/>
       <c r="AZ27" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137382274</t>
+          <t>https://artportalen.se/Sighting/137383002</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>137383002</v>
+        <v>137504305</v>
       </c>
       <c r="B28" t="n">
-        <v>99412</v>
+        <v>99416</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3368,10 +3368,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>678176</v>
+        <v>678371</v>
       </c>
       <c r="R28" t="n">
-        <v>6691424</v>
+        <v>6691166</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3398,12 +3398,12 @@
       </c>
       <c r="Y28" t="inlineStr">
         <is>
-          <t>2026-10-21</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
         <is>
-          <t>2026-10-21</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3429,16 +3429,16 @@
       <c r="AY28" t="inlineStr"/>
       <c r="AZ28" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137383002</t>
+          <t>https://artportalen.se/Sighting/137504305</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>137504305</v>
+        <v>137504400</v>
       </c>
       <c r="B29" t="n">
-        <v>99413</v>
+        <v>99416</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3470,10 +3470,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>678371</v>
+        <v>678367</v>
       </c>
       <c r="R29" t="n">
-        <v>6691166</v>
+        <v>6691116</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3531,16 +3531,16 @@
       <c r="AY29" t="inlineStr"/>
       <c r="AZ29" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137504305</t>
+          <t>https://artportalen.se/Sighting/137504400</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>137504400</v>
+        <v>137505276</v>
       </c>
       <c r="B30" t="n">
-        <v>99413</v>
+        <v>99416</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3572,10 +3572,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>678367</v>
+        <v>678208</v>
       </c>
       <c r="R30" t="n">
-        <v>6691116</v>
+        <v>6691021</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3633,16 +3633,16 @@
       <c r="AY30" t="inlineStr"/>
       <c r="AZ30" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137504400</t>
+          <t>https://artportalen.se/Sighting/137505276</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>137505276</v>
+        <v>137382386</v>
       </c>
       <c r="B31" t="n">
-        <v>99413</v>
+        <v>99461</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3650,21 +3650,21 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>219798</v>
+        <v>219862</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Nästrot</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Epipactis helleborine</t>
+          <t>Neottia nidus-avis</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3674,10 +3674,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>678208</v>
+        <v>678326</v>
       </c>
       <c r="R31" t="n">
-        <v>6691021</v>
+        <v>6691332</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3704,12 +3704,12 @@
       </c>
       <c r="Y31" t="inlineStr">
         <is>
-          <t>2026-10-28</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
         <is>
-          <t>2026-10-28</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3735,38 +3735,38 @@
       <c r="AY31" t="inlineStr"/>
       <c r="AZ31" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137505276</t>
+          <t>https://artportalen.se/Sighting/137382386</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>137382386</v>
+        <v>137505541</v>
       </c>
       <c r="B32" t="n">
-        <v>99457</v>
+        <v>102570</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>219862</v>
+        <v>221235</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Nästrot</t>
+          <t>Vårärt</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Neottia nidus-avis</t>
+          <t>Lathyrus vernus</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(L.) Bernh.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3776,10 +3776,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>678326</v>
+        <v>678288</v>
       </c>
       <c r="R32" t="n">
-        <v>6691332</v>
+        <v>6691054</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3806,12 +3806,12 @@
       </c>
       <c r="Y32" t="inlineStr">
         <is>
-          <t>2026-10-21</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
         <is>
-          <t>2026-10-21</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -3837,38 +3837,38 @@
       <c r="AY32" t="inlineStr"/>
       <c r="AZ32" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137382386</t>
+          <t>https://artportalen.se/Sighting/137505541</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>137505541</v>
+        <v>137383133</v>
       </c>
       <c r="B33" t="n">
-        <v>102567</v>
+        <v>104974</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>221235</v>
+        <v>222412</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Vårärt</t>
+          <t>Tibast</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Lathyrus vernus</t>
+          <t>Daphne mezereum</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(L.) Bernh.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -3878,10 +3878,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>678288</v>
+        <v>678135</v>
       </c>
       <c r="R33" t="n">
-        <v>6691054</v>
+        <v>6691495</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -3908,12 +3908,12 @@
       </c>
       <c r="Y33" t="inlineStr">
         <is>
-          <t>2026-10-28</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
         <is>
-          <t>2026-10-28</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -3939,16 +3939,16 @@
       <c r="AY33" t="inlineStr"/>
       <c r="AZ33" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137505541</t>
+          <t>https://artportalen.se/Sighting/137383133</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>137383133</v>
+        <v>137383165</v>
       </c>
       <c r="B34" t="n">
-        <v>104968</v>
+        <v>104974</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3980,10 +3980,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>678135</v>
+        <v>678105</v>
       </c>
       <c r="R34" t="n">
-        <v>6691495</v>
+        <v>6691485</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4041,16 +4041,16 @@
       <c r="AY34" t="inlineStr"/>
       <c r="AZ34" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137383133</t>
+          <t>https://artportalen.se/Sighting/137383165</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>137383165</v>
+        <v>137381381</v>
       </c>
       <c r="B35" t="n">
-        <v>104968</v>
+        <v>101654</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4058,21 +4058,21 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>222412</v>
+        <v>222498</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Tibast</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Daphne mezereum</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4082,10 +4082,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>678105</v>
+        <v>678430</v>
       </c>
       <c r="R35" t="n">
-        <v>6691485</v>
+        <v>6691223</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4143,16 +4143,16 @@
       <c r="AY35" t="inlineStr"/>
       <c r="AZ35" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137383165</t>
+          <t>https://artportalen.se/Sighting/137381381</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>137381381</v>
+        <v>137383104</v>
       </c>
       <c r="B36" t="n">
-        <v>101650</v>
+        <v>101654</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4184,10 +4184,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>678430</v>
+        <v>678175</v>
       </c>
       <c r="R36" t="n">
-        <v>6691223</v>
+        <v>6691444</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4244,108 +4244,6 @@
       </c>
       <c r="AY36" t="inlineStr"/>
       <c r="AZ36" t="inlineStr">
-        <is>
-          <t>https://artportalen.se/Sighting/137381381</t>
-        </is>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" t="n">
-        <v>137383104</v>
-      </c>
-      <c r="B37" t="n">
-        <v>101650</v>
-      </c>
-      <c r="D37" t="inlineStr">
-        <is>
-          <t>LC</t>
-        </is>
-      </c>
-      <c r="E37" t="n">
-        <v>222498</v>
-      </c>
-      <c r="F37" t="inlineStr">
-        <is>
-          <t>Blåsippa</t>
-        </is>
-      </c>
-      <c r="G37" t="inlineStr">
-        <is>
-          <t>Hepatica nobilis</t>
-        </is>
-      </c>
-      <c r="H37" t="inlineStr">
-        <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I37" t="inlineStr"/>
-      <c r="P37" t="inlineStr">
-        <is>
-          <t>Duderö, Upl</t>
-        </is>
-      </c>
-      <c r="Q37" t="n">
-        <v>678175</v>
-      </c>
-      <c r="R37" t="n">
-        <v>6691444</v>
-      </c>
-      <c r="S37" t="n">
-        <v>10</v>
-      </c>
-      <c r="T37" t="inlineStr">
-        <is>
-          <t>Uppsala</t>
-        </is>
-      </c>
-      <c r="U37" t="inlineStr">
-        <is>
-          <t>Östhammar</t>
-        </is>
-      </c>
-      <c r="V37" t="inlineStr">
-        <is>
-          <t>Uppland</t>
-        </is>
-      </c>
-      <c r="W37" t="inlineStr">
-        <is>
-          <t>Börstil</t>
-        </is>
-      </c>
-      <c r="Y37" t="inlineStr">
-        <is>
-          <t>2026-10-21</t>
-        </is>
-      </c>
-      <c r="AA37" t="inlineStr">
-        <is>
-          <t>2026-10-21</t>
-        </is>
-      </c>
-      <c r="AD37" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE37" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG37" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT37" t="inlineStr"/>
-      <c r="AW37" t="inlineStr">
-        <is>
-          <t>Erland Lindblad</t>
-        </is>
-      </c>
-      <c r="AX37" t="inlineStr">
-        <is>
-          <t>Erland Lindblad</t>
-        </is>
-      </c>
-      <c r="AY37" t="inlineStr"/>
-      <c r="AZ37" t="inlineStr">
         <is>
           <t>https://artportalen.se/Sighting/137383104</t>
         </is>
@@ -4388,7 +4286,6 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ34" r:id="rId33"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ35" r:id="rId34"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ36" r:id="rId35"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ37" r:id="rId36"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
